--- a/output/xlsx/AdministradorDeletaCompatibilidade--GT-.xlsx
+++ b/output/xlsx/AdministradorDeletaCompatibilidade--GT-.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="46">
   <si>
     <t xml:space="preserve">System: </t>
   </si>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">Precondition: </t>
   </si>
   <si>
-    <t>Usuario Administrador esta logado no sistema.</t>
+    <t>Usuario Administrador deve estar logado no sistema.</t>
   </si>
   <si>
     <t>#</t>
@@ -92,70 +92,64 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>Administrador: abre tela inicial do sistema</t>
+    <t>Administrador: Clicar na opcao 'Compatibildiade' no menu da tela principal</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>SYSTEM exibe tela inicial do sistema</t>
-  </si>
-  <si>
-    <t>Administrador: clica na opcao 'Compatibilidades' no menu da tela principal</t>
-  </si>
-  <si>
-    <t>SYSTEM apresenta uma listagem dos Compatibilidades cadastrados no sistema</t>
-  </si>
-  <si>
-    <t>Administrador: clica em algum dos Compatibilidades listados</t>
-  </si>
-  <si>
-    <t>SYSTEM abre a tela de edicao de Compatibilidade</t>
-  </si>
-  <si>
-    <t>Administrador: clica no botao de 'Excluir'</t>
-  </si>
-  <si>
-    <t>SYSTEM exibe popup pedindo Confirmacao de delecao</t>
-  </si>
-  <si>
-    <t>Administrador: confirma delecao</t>
-  </si>
-  <si>
-    <t>SYSTEM notifica que o Compatibilidade foi excluido com sucesso</t>
+    <t>SYSTEM exibe a tela de listagem das Compatibilidades</t>
+  </si>
+  <si>
+    <t>Administrador: clica em Compatibilidade listada</t>
+  </si>
+  <si>
+    <t>SYSTEM exibe a tela de edicao de Compatibilidade</t>
+  </si>
+  <si>
+    <t>Administrador: clica em botao 'Deletar'</t>
+  </si>
+  <si>
+    <t>SYSTEM abre popup de confirmacao de delecao</t>
+  </si>
+  <si>
+    <t>Administrador: confirma que deseja deletar clicando em 'Sim'</t>
+  </si>
+  <si>
+    <t>SYSTEM notifica usuario que os nova Compatibilidade foi deletada com sucesso</t>
   </si>
   <si>
     <t xml:space="preserve">Postcondition: </t>
   </si>
   <si>
-    <t>O Compatibilidade foi excluida com sucesso.</t>
+    <t>Compatibilidade foi deletada.</t>
   </si>
   <si>
     <t>TC2</t>
   </si>
   <si>
-    <t>Alternative Flow 1: Volta para tela inicial de sistema</t>
-  </si>
-  <si>
-    <t>Administrador: clica no botao Voltar</t>
+    <t>Alternative Flow 1: Navega pelas paginas da lista</t>
+  </si>
+  <si>
+    <t>Administrador: navega nas paginas da lista</t>
   </si>
   <si>
     <t>TC3</t>
   </si>
   <si>
-    <t>Alternative Flow 2: Cancela delecao de Compatibilidade</t>
-  </si>
-  <si>
-    <t>Administrador: clica no botao 'Cancelar'</t>
+    <t>Alternative Flow 2: Usuario ordena lista de Compatibilidades</t>
+  </si>
+  <si>
+    <t>Administrador: ordenas as Compatibilidades por seus atributos</t>
   </si>
   <si>
     <t>TC4</t>
   </si>
   <si>
-    <t>Alternative Flow 3: Fecha popup de confirmacao de delecao</t>
-  </si>
-  <si>
-    <t>Administrador: clica no botao 'Cancelar' do popup</t>
+    <t>Alternative Flow 3: Cancela delecao</t>
+  </si>
+  <si>
+    <t>Administrador: clica no botao 'Cancelar' de popup</t>
   </si>
 </sst>
 </file>
@@ -247,13 +241,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="60.86328125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="61.0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="21.8984375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="63.953125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="64.5078125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="30.5234375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="17.578125" customWidth="true" bestFit="true"/>
   </cols>
@@ -431,92 +425,92 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="B14" t="s" s="3">
+      <c r="A14" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="C14" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D14" t="s" s="3">
+      <c r="B14" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="E14" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F14" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="1">
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="B17" t="s" s="0">
         <v>37</v>
       </c>
-      <c r="B15" t="s" s="0">
-        <v>38</v>
+      <c r="C17" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E17" t="s" s="1">
+        <v>14</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="1">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>39</v>
-      </c>
-      <c r="C18" t="s" s="1">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="E18" t="s" s="1">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="1">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="E19" t="s" s="1">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="s" s="1">
-        <v>18</v>
-      </c>
-      <c r="B20" t="s" s="0">
-        <v>19</v>
+      <c r="A20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>25</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="D21" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="E21" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F21" t="s" s="2">
-        <v>25</v>
+      <c r="A21" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B21" t="s" s="3">
+        <v>26</v>
+      </c>
+      <c r="C21" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D21" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E21" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F21" t="s" s="3">
+        <v>27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n" s="4">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="B22" t="s" s="3">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s" s="3">
         <v>27</v>
@@ -533,7 +527,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n" s="4">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="B23" t="s" s="3">
         <v>29</v>
@@ -553,16 +547,16 @@
     </row>
     <row r="24">
       <c r="A24" t="n" s="4">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="B24" t="s" s="3">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C24" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D24" t="s" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E24" t="s" s="3">
         <v>27</v>
@@ -573,16 +567,16 @@
     </row>
     <row r="25">
       <c r="A25" t="n" s="4">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="B25" t="s" s="3">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C25" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D25" t="s" s="3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E25" t="s" s="3">
         <v>27</v>
@@ -592,138 +586,138 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="B26" t="s" s="3">
-        <v>31</v>
-      </c>
-      <c r="C26" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D26" t="s" s="3">
-        <v>32</v>
-      </c>
-      <c r="E26" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F26" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="B27" t="s" s="3">
-        <v>33</v>
-      </c>
-      <c r="C27" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D27" t="s" s="3">
-        <v>34</v>
-      </c>
-      <c r="E27" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F27" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n" s="4">
-        <v>7.0</v>
-      </c>
-      <c r="B28" t="s" s="3">
+      <c r="A26" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="C28" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D28" t="s" s="3">
+      <c r="B26" t="s" s="0">
         <v>36</v>
-      </c>
-      <c r="E28" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F28" t="s" s="3">
-        <v>27</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="1">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>38</v>
+        <v>40</v>
+      </c>
+      <c r="C29" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E29" t="s" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="E30" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="1">
+        <v>18</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>19</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B32" t="s" s="0">
+      <c r="A32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D32" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="E32" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="F32" t="s" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B33" t="s" s="3">
+        <v>26</v>
+      </c>
+      <c r="C33" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D33" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E33" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F33" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="B34" t="s" s="3">
         <v>42</v>
       </c>
-      <c r="C32" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E32" t="s" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s" s="0">
-        <v>43</v>
-      </c>
-      <c r="E33" t="s" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="1">
-        <v>18</v>
-      </c>
-      <c r="B34" t="s" s="0">
-        <v>19</v>
+      <c r="C34" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D34" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E34" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F34" t="s" s="3">
+        <v>27</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="D35" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="E35" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F35" t="s" s="2">
-        <v>25</v>
+      <c r="A35" t="n" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="B35" t="s" s="3">
+        <v>29</v>
+      </c>
+      <c r="C35" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D35" t="s" s="3">
+        <v>30</v>
+      </c>
+      <c r="E35" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F35" t="s" s="3">
+        <v>27</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n" s="4">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="B36" t="s" s="3">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C36" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D36" t="s" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E36" t="s" s="3">
         <v>27</v>
@@ -734,16 +728,16 @@
     </row>
     <row r="37">
       <c r="A37" t="n" s="4">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="B37" t="s" s="3">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C37" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D37" t="s" s="3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E37" t="s" s="3">
         <v>27</v>
@@ -753,178 +747,178 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="B38" t="s" s="3">
-        <v>31</v>
-      </c>
-      <c r="C38" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D38" t="s" s="3">
-        <v>32</v>
-      </c>
-      <c r="E38" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F38" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="B39" t="s" s="3">
+      <c r="A38" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C41" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E41" t="s" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s" s="0">
         <v>44</v>
       </c>
-      <c r="C39" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D39" t="s" s="3">
-        <v>30</v>
-      </c>
-      <c r="E39" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F39" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="B40" t="s" s="3">
-        <v>31</v>
-      </c>
-      <c r="C40" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D40" t="s" s="3">
-        <v>32</v>
-      </c>
-      <c r="E40" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F40" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="B41" t="s" s="3">
-        <v>33</v>
-      </c>
-      <c r="C41" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D41" t="s" s="3">
-        <v>34</v>
-      </c>
-      <c r="E41" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F41" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n" s="4">
-        <v>7.0</v>
-      </c>
-      <c r="B42" t="s" s="3">
-        <v>35</v>
-      </c>
-      <c r="C42" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D42" t="s" s="3">
-        <v>36</v>
-      </c>
-      <c r="E42" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F42" t="s" s="3">
-        <v>27</v>
+      <c r="E42" t="s" s="1">
+        <v>17</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="1">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B43" t="s" s="0">
-        <v>38</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D44" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="E44" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="F44" t="s" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B45" t="s" s="3">
+        <v>26</v>
+      </c>
+      <c r="C45" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D45" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E45" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F45" t="s" s="3">
+        <v>27</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B46" t="s" s="0">
+      <c r="A46" t="n" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="B46" t="s" s="3">
+        <v>29</v>
+      </c>
+      <c r="C46" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D46" t="s" s="3">
+        <v>30</v>
+      </c>
+      <c r="E46" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F46" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="B47" t="s" s="3">
+        <v>31</v>
+      </c>
+      <c r="C47" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D47" t="s" s="3">
+        <v>32</v>
+      </c>
+      <c r="E47" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F47" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="B48" t="s" s="3">
         <v>45</v>
       </c>
-      <c r="C46" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E46" t="s" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s" s="0">
-        <v>46</v>
-      </c>
-      <c r="E47" t="s" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s" s="1">
-        <v>18</v>
-      </c>
-      <c r="B48" t="s" s="0">
-        <v>19</v>
+      <c r="C48" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D48" t="s" s="3">
+        <v>30</v>
+      </c>
+      <c r="E48" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F48" t="s" s="3">
+        <v>27</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="D49" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="E49" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F49" t="s" s="2">
-        <v>25</v>
+      <c r="A49" t="n" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="B49" t="s" s="3">
+        <v>31</v>
+      </c>
+      <c r="C49" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D49" t="s" s="3">
+        <v>32</v>
+      </c>
+      <c r="E49" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F49" t="s" s="3">
+        <v>27</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n" s="4">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="B50" t="s" s="3">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C50" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D50" t="s" s="3">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E50" t="s" s="3">
         <v>27</v>
@@ -934,131 +928,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="B51" t="s" s="3">
-        <v>29</v>
-      </c>
-      <c r="C51" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D51" t="s" s="3">
-        <v>30</v>
-      </c>
-      <c r="E51" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F51" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="B52" t="s" s="3">
-        <v>31</v>
-      </c>
-      <c r="C52" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D52" t="s" s="3">
-        <v>32</v>
-      </c>
-      <c r="E52" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F52" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="B53" t="s" s="3">
-        <v>33</v>
-      </c>
-      <c r="C53" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D53" t="s" s="3">
-        <v>34</v>
-      </c>
-      <c r="E53" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F53" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="B54" t="s" s="3">
-        <v>47</v>
-      </c>
-      <c r="C54" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D54" t="s" s="3">
-        <v>32</v>
-      </c>
-      <c r="E54" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F54" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="B55" t="s" s="3">
-        <v>33</v>
-      </c>
-      <c r="C55" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D55" t="s" s="3">
-        <v>34</v>
-      </c>
-      <c r="E55" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F55" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n" s="4">
-        <v>7.0</v>
-      </c>
-      <c r="B56" t="s" s="3">
+      <c r="A51" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="C56" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D56" t="s" s="3">
+      <c r="B51" t="s" s="0">
         <v>36</v>
-      </c>
-      <c r="E56" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F56" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="1">
-        <v>37</v>
-      </c>
-      <c r="B57" t="s" s="0">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
